--- a/data/example_data.xlsx
+++ b/data/example_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\major\Documents\KAZAKHSTAN\Olymp_inventory_forecast\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43DE42A-831F-45DF-A0B4-20B48608926C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9E5EDD-B6B6-493C-A3B6-4BF7C9E56DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{107DBBD2-B6D7-409B-8162-14A305E781F3}"/>
   </bookViews>
@@ -804,10 +804,10 @@
         <v>700</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2">
+      <c r="H9" s="2">
         <v>700</v>
       </c>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -887,8 +887,7 @@
         <v>1690</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="3">
+      <c r="H12" s="3">
         <v>1690</v>
       </c>
     </row>
@@ -912,8 +911,7 @@
       <c r="G13" s="3">
         <v>25200</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="3">
+      <c r="H13" s="3">
         <v>25200</v>
       </c>
     </row>
@@ -962,8 +960,7 @@
         <v>1180</v>
       </c>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="3">
+      <c r="H15" s="3">
         <v>1180</v>
       </c>
     </row>
@@ -1068,8 +1065,7 @@
         <v>15680</v>
       </c>
       <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="3">
+      <c r="H19" s="3">
         <v>15680</v>
       </c>
     </row>
@@ -1251,8 +1247,7 @@
         <v>2310</v>
       </c>
       <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="3">
+      <c r="H26" s="3">
         <v>2310</v>
       </c>
     </row>
@@ -1357,8 +1352,7 @@
         <v>14610</v>
       </c>
       <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="3">
+      <c r="H30" s="3">
         <v>14610</v>
       </c>
     </row>
@@ -1461,8 +1455,7 @@
         <v>2588</v>
       </c>
       <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="3">
+      <c r="H34" s="3">
         <v>2588</v>
       </c>
     </row>
